--- a/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件四.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件四.xlsx
@@ -1,179 +1,565 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="121">
+  <si>
+    <t>角色编号</t>
+  </si>
+  <si>
+    <t>台词编号</t>
+  </si>
+  <si>
+    <t>台词 / 旁白文本</t>
+  </si>
+  <si>
+    <t>立绘 / 动作提示</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>晚上，你正坐在电脑前进行 “电竞社交与情感代偿” 视频的精修</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>剪辑软件的时间轴上密密麻麻地排列着音频轨道和视频轨道，你已经改到第四版了</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>为了保证听觉效果，你正戴着耳机，和闺蜜许映月开着语音通话，让她帮忙试听初版配音</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>“我去…… 宝宝，你从哪找的？！这低音炮，这温柔的语气，也太有情绪价值了吧！”</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>她的声音从耳机里炸出来，带着一种发现新大陆的兴奋</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>“听得我鸡皮疙瘩都起来了！不仁义啊，偷偷吃这么好竟然不告诉我！”</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>你端起桌上的咖啡抿了一口，目光依旧冷静地盯着剪辑软件的音频轨道</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>“人家挺忙的，以后有机会再介绍你们认识。”</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>“不过现在的声卡特发达，网上声音好听，现实里指不定是个抠脚大汉呢，你可得小心点。”</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>“好，我会注意的。”</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>和许映月闲聊了几句后，你挂断了语音。正准备导出视频，放在一旁的手机屏幕倏地亮了</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>是时安发来的消息</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>你点开一看，是一张没有配文的照片</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>照片的背景看着像是高校食堂，镜头对着的桌面上放着一份夜宵炒面，铁盘子装着，筷子搁在边沿上，还冒着热气</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>而旁边，整整齐齐地码着几本厚厚的专业书，书脊上有折痕，封面边角有些卷，像是被反复翻过很多次</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>画面边缘，是不经意间露出的骨节分明的手腕。很瘦，皮肤在食堂的日光灯下显得有些苍白</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>两秒后，他的文字消息弹了出来</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>“感谢老板的支持，下个学期的学费和生活费，我终于攒够了。今天可以稍微放纵一下，加个餐。”</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>你看着那张照片，立刻看懂了这张照片背后的潜台词</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>这不仅仅是一份日常分享，这是他在向你汇报战果，更是他在向你这个成熟可靠的前辈汇报战果</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>他在告诉你：我听进去了，我会好好生活</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>你放下咖啡杯，回了一个 “干杯” 的表情包，然后打字</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>“效率很高，看来你把我那天的话听进去了。祝贺你，找到了自己的生活方式。”</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>你按下发送键。聊天框顶部的 “对方正在输入中” 闪烁了很久</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>很久，久到你以为他遇到了网络延迟，或者打了很长很长的一段话又删掉了</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>终于，一条语音发了过来，你点开语音</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>他的语速放得很慢，背景音里还有食堂风扇转动的嗡嗡声，以及远处隐约的餐盘碰撞声</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>他的声音带着一种孤注一掷的试探与忐忑，像是站在悬崖边上，不知道跳下去是飞翔还是坠落</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>“其实…… 这段时间我一直在想，网络那端那个冷静又清醒的你，在现实中到底是个什么样的人。”</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>他深吸了一口气，带着一种怕被拒绝的小心翼翼</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>“这周末，我可以请你见个面吗？”</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>“不走平台的单子，也不计费。这一次，我想以我最真实的身份，去认识你。”</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>语音播放完毕，你看着屏幕上那条语音的波形图，手指悬在键盘上方</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>【抉择选项】以朋友的名义反邀请</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>对于这个在你眼皮子底下成长起来的年轻人，你不反感给予他一些额外的奖励</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>作为更成熟的一方，你并不介意顺水推舟，去验证一下这份隔着网线的羁绊，在现实中是否依然有趣</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>你的手指在键盘上飞快地敲击</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>“可以，刚好可以做一期面基 Vlog。如果你愿意过来我这边，我可以作为东道主，安排周末的行程。”</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>不是约会，不是暧昧，只是一个成熟前辈对一个努力后辈的鼓励</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>但你知道，你心里也有一丝好奇，也或许并非一丝</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>你等他的回复，这次没有 “对方正在输入中” 的闪烁。回复几乎是瞬间弹出来的</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>“好，我去买票。老板，我很期待。”</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>你没有要求他更改对你的称谓，出于一些本能习惯，你依然考虑着给自己、给你们的关系留一条退路</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>【抉择选项】以工作的名义邀请</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>你翻看了一下备忘录里的行程安排</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>线下见面意味着打破安全距离，许映月刚才的调侃也并非全无道理</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>虽然你知道他不是，但你也不得不承认，网线和现实是两回事</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>但如果将这次见面置于你的可控范围内，作为一次补充素材的会面，也未尝不可</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>很快，你做出了利益最大化且边界清晰的决定</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>你的手指在键盘上敲击，语气公事公办</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>“刚好这周末我需要去一趟游乐园采风，补几个外景的镜头。如果你愿意当拿反光板的苦力，我并不介意。”</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>你用一种顺便的方式，巧妙地化解这次邀约中过于私人的暧昧感</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>不是见面，是工作；不是约会，是帮忙</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>你等他的回复，“对方正在输入中” 闪了几下，然后</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>“没问题，保证随叫随到，绝不耽误老板工作。”</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>他并没有因为你的冷静而气馁，反而十分痛快地答应了下来</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,156 +859,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,74 +1067,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1323,713 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="104.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>